--- a/src/attributions/attributions_ig_traj_221.xlsx
+++ b/src/attributions/attributions_ig_traj_221.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.3050611304352649</v>
+        <v>0.01105733679810535</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4726393428925968</v>
+        <v>0.09492235922318808</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09978968163162688</v>
+        <v>0.05241077213281141</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.009103980469607182</v>
+        <v>0.04885570523122351</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3255603886305961</v>
+        <v>0.08001056648971686</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04351261490959426</v>
+        <v>0.0768907518445574</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1616,58 +1616,58 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.05221420602365129</v>
+        <v>-0.02751743102123977</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2066874781147941</v>
+        <v>-0.03090444017796179</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1158859184676732</v>
+        <v>-0.05578725720988256</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.02148130002792051</v>
+        <v>0.01128559917377321</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.08519283491813977</v>
+        <v>0.06837618028765098</v>
       </c>
       <c r="AE3" t="n">
         <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.05194714172996148</v>
+        <v>-0.0002464671649351817</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1676,25 +1676,25 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.03664926907665584</v>
+        <v>-0.05689211426986129</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.1071856748632241</v>
+        <v>0.01912625862279102</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1462916610838306</v>
+        <v>-0.1360143787353399</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.02501868363225625</v>
+        <v>-0.1162426756362581</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.380761975694141</v>
+        <v>0.006112001426590906</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4258905991455501</v>
+        <v>-0.1303192732890349</v>
       </c>
       <c r="AY3" t="n">
         <v>-0</v>
@@ -1724,52 +1724,52 @@
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.1822166491175117</v>
+        <v>0.07928239632595613</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.01598688570218473</v>
+        <v>0.0764856427023614</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.02748464565704469</v>
+        <v>0.2086804589744901</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.131519305183768</v>
+        <v>-0.004301510086392232</v>
       </c>
       <c r="BM3" t="n">
         <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1184769285999194</v>
+        <v>-0.0178478584820857</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.3914418238922932</v>
+        <v>-0.05807352550261586</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
@@ -1778,31 +1778,31 @@
         <v>-0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.01459139548845959</v>
+        <v>-0.04214019699273892</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1065056599616347</v>
+        <v>-0.01832206538957832</v>
       </c>
       <c r="BX3" t="n">
         <v>-0</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.3217759484579982</v>
+        <v>-0.06054557328135234</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
@@ -1811,268 +1811,268 @@
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.03124746486421689</v>
+        <v>-0.01735478541287595</v>
       </c>
       <c r="CE3" t="n">
         <v>-0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.1213285467856244</v>
+        <v>-0.02770694948772584</v>
       </c>
       <c r="CG3" t="n">
         <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.06239868174711793</v>
+        <v>0.000958599184855567</v>
       </c>
       <c r="CI3" t="n">
         <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.1645153653998349</v>
+        <v>0.03269851177978993</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1122127011319588</v>
+        <v>0.01055142892623163</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.3443486107156875</v>
+        <v>-0.03859124480364414</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.01412971291664059</v>
+        <v>-0.005113614720836921</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.09859092807838056</v>
+        <v>-0.02368628252360203</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.009379685930567703</v>
+        <v>-0.01397192588420078</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1077363748596687</v>
+        <v>0.004457147337526232</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.006243889230513396</v>
+        <v>0.00221309534780764</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.02387840545177806</v>
+        <v>0.1778624516857568</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.2607999511367259</v>
+        <v>0.1147422914637868</v>
       </c>
       <c r="DO3" t="n">
         <v>-0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.05403832432986554</v>
+        <v>-0.01260580141182355</v>
       </c>
       <c r="DQ3" t="n">
         <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.2097052349936486</v>
+        <v>0.1056083916601118</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.07509154097535253</v>
+        <v>0.03785182415774023</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.007401668338202348</v>
+        <v>-0.01757182536118371</v>
       </c>
       <c r="DZ3" t="n">
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.1040253827474424</v>
+        <v>0.1472593610064115</v>
       </c>
       <c r="EB3" t="n">
         <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.03412716965529089</v>
+        <v>-0.06970030949097941</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.2580930429170445</v>
+        <v>-0.01526844666962747</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.06653279658850078</v>
+        <v>0.03970233405009659</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.1625514634590845</v>
+        <v>0.008376039239681049</v>
       </c>
       <c r="EP3" t="n">
         <v>-0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.04151321224487386</v>
+        <v>0.02369406104940863</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.06729387113410759</v>
+        <v>-0.05986475795664262</v>
       </c>
       <c r="ET3" t="n">
         <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.002804224805813155</v>
+        <v>-0.01388324610564105</v>
       </c>
       <c r="EY3" t="n">
         <v>-0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.1127818497219317</v>
+        <v>-0.03094268243733493</v>
       </c>
       <c r="FA3" t="n">
         <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.002819387887120645</v>
+        <v>-0.01109807061390485</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.09861527424957434</v>
+        <v>0.0661848116365519</v>
       </c>
       <c r="FH3" t="n">
         <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.03499493117741827</v>
+        <v>-0.07820925691334374</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.0969900162116122</v>
+        <v>0.08855328511627564</v>
       </c>
       <c r="FL3" t="n">
         <v>0</v>
       </c>
       <c r="FM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN3" t="n">
         <v>0</v>
@@ -2081,43 +2081,43 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0.02201891928141997</v>
+        <v>0.1010043947690485</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR3" t="n">
-        <v>-0.0001615682892156425</v>
+        <v>-0.0002290794525664508</v>
       </c>
       <c r="FS3" t="n">
         <v>-0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.0015806755276241</v>
+        <v>-0.002748182457880917</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
         <v>0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.01510767271974528</v>
+        <v>0.008178838778180661</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1063723644036862</v>
+        <v>0.03717653218115689</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
@@ -2129,10 +2129,10 @@
         <v>-0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,16 +2140,16 @@
         <v>-0</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.4241253634342238</v>
+        <v>-0.4784861353032979</v>
       </c>
       <c r="C4" t="n">
         <v>-0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3032583689442004</v>
+        <v>0.1040970141762822</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3311817726706877</v>
+        <v>0.212009984749517</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -2167,19 +2167,19 @@
         <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2277350909413665</v>
+        <v>-0.3560568816687021</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1818651587271091</v>
+        <v>0.2425906940874178</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3048929388792337</v>
+        <v>0.2714825468312645</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -2191,28 +2191,28 @@
         <v>-0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1705371058137986</v>
+        <v>-0.03043558146388091</v>
       </c>
       <c r="U4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03190317814942223</v>
+        <v>0.06860226059082199</v>
       </c>
       <c r="W4" t="n">
-        <v>0.07586295370500065</v>
+        <v>0.007515932351973765</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>-0</v>
@@ -2221,43 +2221,43 @@
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.132041280087239</v>
+        <v>-0.1630406826554815</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.04652699199262338</v>
+        <v>0.1029663240091698</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.02241695841358442</v>
+        <v>-0.009037899876713676</v>
       </c>
       <c r="AG4" t="n">
         <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-0.192344567657654</v>
+        <v>-0.312890263589678</v>
       </c>
       <c r="AM4" t="n">
         <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.03145357094804983</v>
+        <v>0.08789608941795693</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1029357818634403</v>
+        <v>-0.2342700862225758</v>
       </c>
       <c r="AP4" t="n">
         <v>-0</v>
@@ -2266,34 +2266,34 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.5043156887187102</v>
+        <v>-0.4669308430376339</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.186903174316421</v>
+        <v>0.1387959648579228</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1087929246506127</v>
+        <v>0.3027134877083426</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
@@ -2302,25 +2302,25 @@
         <v>-0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.02340165574407702</v>
+        <v>0.04257953543672872</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.0192152662613653</v>
+        <v>0.03249337376190212</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.4033826027542541</v>
+        <v>0.197558136214134</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>-0</v>
@@ -2329,46 +2329,46 @@
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.003716683223234377</v>
+        <v>0.08675326521666837</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.04127150395093469</v>
+        <v>0.05588813184293363</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.07010142515816149</v>
+        <v>0.006181314306225992</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
         <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.2532633965094973</v>
+        <v>-0.3114761149259161</v>
       </c>
       <c r="BW4" t="n">
         <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.07234269478293086</v>
+        <v>0.1619186817432441</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.2031648354844097</v>
+        <v>0.095143883864017</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA4" t="n">
         <v>0</v>
@@ -2383,76 +2383,76 @@
         <v>0</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.1009534333123384</v>
+        <v>0.3072636421279983</v>
       </c>
       <c r="CF4" t="n">
         <v>0</v>
       </c>
       <c r="CG4" t="n">
-        <v>-0.03581865970345348</v>
+        <v>-0.07513674704109286</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.03546184322032823</v>
+        <v>0.00148278877830315</v>
       </c>
       <c r="CI4" t="n">
         <v>0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>-0</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.06815956606179382</v>
+        <v>0.1912943015571889</v>
       </c>
       <c r="CO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.06507911912386975</v>
+        <v>-0.1536027735697041</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.02859305627715869</v>
+        <v>-0.07939178823953306</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT4" t="n">
         <v>0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
         <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.08816711652087875</v>
+        <v>0.2970119036512189</v>
       </c>
       <c r="CX4" t="n">
         <v>-0</v>
       </c>
       <c r="CY4" t="n">
-        <v>-0.06406959025953737</v>
+        <v>-0.08444987821364476</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.02769768651015489</v>
+        <v>-0.02491862878322315</v>
       </c>
       <c r="DA4" t="n">
         <v>-0</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
         <v>0</v>
@@ -2464,22 +2464,22 @@
         <v>-0</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.1344433541955707</v>
+        <v>0.1159042487588008</v>
       </c>
       <c r="DG4" t="n">
         <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.0003197722076182109</v>
+        <v>0.006340662908376927</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0002511463139896309</v>
+        <v>-0.002886904506414238</v>
       </c>
       <c r="DJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>-0</v>
@@ -2491,22 +2491,22 @@
         <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.1838751153126888</v>
+        <v>0.1601398718046013</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.06372833872714523</v>
+        <v>-0.08720747503912843</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01026111816626162</v>
+        <v>0.03105528041275032</v>
       </c>
       <c r="DS4" t="n">
         <v>-0</v>
       </c>
       <c r="DT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.000339961817174433</v>
+        <v>-0.1025486487195947</v>
       </c>
       <c r="DY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.09762849780572053</v>
+        <v>-0.1172512538587384</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.1101543461112237</v>
+        <v>-0.2078797004802175</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC4" t="n">
         <v>0</v>
@@ -2545,16 +2545,16 @@
         <v>-0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.1041893524643479</v>
+        <v>0.2299729023488895</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>-0.130084279672901</v>
+        <v>-0.02428535991892315</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.06276627842019018</v>
+        <v>-0.01035598831298894</v>
       </c>
       <c r="EK4" t="n">
         <v>0</v>
@@ -2563,25 +2563,25 @@
         <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.06882881144067128</v>
+        <v>0.1748315229835959</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.02905283851749193</v>
+        <v>-0.07573797184035244</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.05184966463845747</v>
+        <v>-0.07633279488697226</v>
       </c>
       <c r="ET4" t="n">
         <v>0</v>
@@ -2593,28 +2593,28 @@
         <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
         <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.07262907738050278</v>
+        <v>0.3489108302848656</v>
       </c>
       <c r="EZ4" t="n">
         <v>0</v>
       </c>
       <c r="FA4" t="n">
-        <v>-0.0603192514074543</v>
+        <v>-0.09785922344140693</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.02688294094697217</v>
+        <v>-0.01322569658547916</v>
       </c>
       <c r="FC4" t="n">
         <v>0</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>-0</v>
@@ -2623,22 +2623,22 @@
         <v>0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.01595599704283748</v>
+        <v>0.198691334399448</v>
       </c>
       <c r="FI4" t="n">
         <v>0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>-0.1571212562722661</v>
+        <v>-0.1138513433247438</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.04746426537126881</v>
+        <v>-0.1464640145011637</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>-0</v>
@@ -2647,31 +2647,31 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP4" t="n">
         <v>0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.009452389438714692</v>
+        <v>-0.03102662870096302</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.01215199992931176</v>
+        <v>-0.1861168669206725</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.002378694587652986</v>
+        <v>0.0003616443555047529</v>
       </c>
       <c r="FU4" t="n">
         <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
         <v>-0</v>
@@ -2680,13 +2680,13 @@
         <v>-0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.02057229452813161</v>
+        <v>0.1530132319543094</v>
       </c>
       <c r="GA4" t="n">
         <v>-0</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.08139137662324451</v>
+        <v>0.02586121243635637</v>
       </c>
       <c r="GC4" t="n">
         <v>-0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,16 +2709,16 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.3595239659945326</v>
+        <v>-0.3737637328004914</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1918948061953517</v>
+        <v>0.1326478602353585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.217961686878524</v>
+        <v>0.07984689236739811</v>
       </c>
       <c r="F5" t="n">
         <v>-0</v>
@@ -2730,25 +2730,25 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.290603672443886</v>
+        <v>-0.4559974253514154</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2105292914795927</v>
+        <v>0.223032096262105</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2389788726610567</v>
+        <v>0.1539367503506809</v>
       </c>
       <c r="O5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -2763,25 +2763,25 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1015994294792082</v>
+        <v>-0.0402388324492669</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01694052201451101</v>
+        <v>0.01267256161566748</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.04183647001244236</v>
+        <v>-0.005544661424828436</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
@@ -2790,22 +2790,22 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.1524543817303817</v>
+        <v>-0.01986218768638529</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.05730643156480612</v>
+        <v>0.1338706937573633</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.03112473842292171</v>
+        <v>-0.2222037577602377</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -2814,76 +2814,76 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.03530618224662264</v>
+        <v>-0.1467362683141169</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.04496369266459647</v>
+        <v>0.03771858075953894</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.07773047799036843</v>
+        <v>-0.2313778420852493</v>
       </c>
       <c r="AP5" t="n">
         <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
         <v>-0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.2823760744888923</v>
+        <v>-0.2428530737293749</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.009386233642463646</v>
+        <v>0.140834232216819</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.01912585227520819</v>
+        <v>0.02256290232743481</v>
       </c>
       <c r="AY5" t="n">
         <v>-0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01270378074326078</v>
+        <v>0.05066757266978159</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.1947370835745189</v>
+        <v>0.01267303549555298</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.2801864307627785</v>
+        <v>0.131204742198662</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI5" t="n">
         <v>-0</v>
@@ -2898,16 +2898,16 @@
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.09746939744970234</v>
+        <v>0.1121550478169164</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.03966367599017617</v>
+        <v>0.08290456634644046</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.1006469971429728</v>
+        <v>0.001854649371135884</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
@@ -2925,25 +2925,25 @@
         <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.2214552231237848</v>
+        <v>-0.1967383025962886</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.001954980983664282</v>
+        <v>0.06910249671461589</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.04295490695730891</v>
+        <v>-0.0085159241749709</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
@@ -2952,25 +2952,25 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.09111559250187642</v>
+        <v>0.1941410410625169</v>
       </c>
       <c r="CF5" t="n">
         <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.04630099311145542</v>
+        <v>-0.05770707510185234</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.002501104486842532</v>
+        <v>-0.004755495526076575</v>
       </c>
       <c r="CI5" t="n">
         <v>0</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>0</v>
@@ -2979,19 +2979,19 @@
         <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.03036194770759994</v>
+        <v>0.089814116304601</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.06177633397348618</v>
+        <v>-0.08566313376769037</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.08264093758651204</v>
+        <v>-0.03688885645439984</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
@@ -3006,22 +3006,22 @@
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.08768772856841285</v>
+        <v>0.203680935099142</v>
       </c>
       <c r="CX5" t="n">
         <v>-0</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.06427216599515229</v>
+        <v>-0.05883352196937213</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.003251567564702623</v>
+        <v>-0.03258943965871855</v>
       </c>
       <c r="DA5" t="n">
         <v>-0</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
@@ -3033,52 +3033,52 @@
         <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1674791704590838</v>
+        <v>0.1516227042501961</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.05120534549396998</v>
+        <v>-0.02342471104732869</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.008569236863323306</v>
+        <v>-0.000970404644517681</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL5" t="n">
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0444027720261606</v>
+        <v>0.09032915425264003</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.03951346969164644</v>
+        <v>-0.04203099856430466</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.06924336164510286</v>
+        <v>0.02707078849941816</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT5" t="n">
         <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,22 +3087,22 @@
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.1020258637098203</v>
+        <v>0.04218837314236253</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.09150862549650279</v>
+        <v>0.04949671606083903</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.05065278254419057</v>
+        <v>0.006867971764129158</v>
       </c>
       <c r="EB5" t="n">
         <v>0</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED5" t="n">
         <v>-0</v>
@@ -3114,22 +3114,22 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.05382829121024003</v>
+        <v>0.2267285513372236</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.04169300521635982</v>
+        <v>-0.0568662035802833</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.1036737619249987</v>
+        <v>-0.03789969876844101</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
         <v>0</v>
@@ -3138,28 +3138,28 @@
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0004639062558998706</v>
+        <v>-0.1168263580159574</v>
       </c>
       <c r="EQ5" t="n">
         <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.03281302057021471</v>
+        <v>-0.01012929929656321</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02831961310528018</v>
+        <v>0.004782772460820705</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
         <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
@@ -3168,16 +3168,16 @@
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.09068410370469708</v>
+        <v>0.2302553806432373</v>
       </c>
       <c r="EZ5" t="n">
         <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0.05954802278726774</v>
+        <v>-0.0707934113191805</v>
       </c>
       <c r="FB5" t="n">
-        <v>-0.005773934316406578</v>
+        <v>-0.0006280483128592738</v>
       </c>
       <c r="FC5" t="n">
         <v>0</v>
@@ -3186,52 +3186,52 @@
         <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG5" t="n">
         <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.05169731641457217</v>
+        <v>0.08428186888562736</v>
       </c>
       <c r="FI5" t="n">
         <v>0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.08810583646586569</v>
+        <v>0.1085450814762721</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.04179208425015184</v>
+        <v>0.03676015370198812</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.02522769737549652</v>
+        <v>0.1785516605937419</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.03322027598198776</v>
+        <v>0.01260390136827294</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.009205554983633504</v>
+        <v>-0.05637390529607172</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
@@ -3240,37 +3240,37 @@
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.05225639164725931</v>
+        <v>0.2022148667834</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.06616922842704878</v>
+        <v>-0.001531745628289719</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4870340664615532</v>
+        <v>0.3451182324101872</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -3287,16 +3287,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1171038079518017</v>
+        <v>-0.02415007276200525</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4436249964418046</v>
+        <v>-0.1423975481477552</v>
       </c>
       <c r="G6" t="n">
         <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3305,7 +3305,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4564442769178869</v>
+        <v>0.4556398729406052</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3314,25 +3314,25 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.05570592675916219</v>
+        <v>-0.1057542333602102</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4518573142021146</v>
+        <v>-0.2037387679502438</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03678668043720053</v>
+        <v>0.0994621737550056</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3341,16 +3341,16 @@
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.08439262822239568</v>
+        <v>-0.1181451646230026</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.01567068857811676</v>
+        <v>-0.01165391202914747</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -3359,19 +3359,19 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.02363507836424826</v>
+        <v>-0.03181093238320283</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.01012467495818293</v>
+        <v>-0.2802260515972894</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.03447034086699631</v>
+        <v>-0.0004806981102348303</v>
       </c>
       <c r="AH6" t="n">
         <v>-0</v>
@@ -3386,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.08346482370634739</v>
+        <v>0.03391320067782991</v>
       </c>
       <c r="AM6" t="n">
         <v>-0</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.001425139274130004</v>
+        <v>-0.04382687751844315</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.08288815890890448</v>
+        <v>0.01800998439388342</v>
       </c>
       <c r="AQ6" t="n">
         <v>-0</v>
@@ -3410,10 +3410,10 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4142823062989933</v>
+        <v>0.490930550772916</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
@@ -3422,16 +3422,16 @@
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.07056162875261536</v>
+        <v>-0.2412630341333792</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.2195072107427806</v>
+        <v>-0.1060183635823349</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>0</v>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.1084983479853896</v>
+        <v>-0.03244371999040717</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
@@ -3449,52 +3449,52 @@
         <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1511296373082835</v>
+        <v>-0.01743696709524062</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.1920463743209763</v>
+        <v>-0.08854328880803962</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.1430673738132707</v>
+        <v>0.0555858806580355</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.003506804419984493</v>
+        <v>0.08095184223925117</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01774829638850664</v>
+        <v>-0.0353695774531211</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2174578064331273</v>
+        <v>0.2645884054932645</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.07027843473932166</v>
+        <v>-0.07607225122038919</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.1317131469424722</v>
+        <v>-0.1065766498934343</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
@@ -3521,22 +3521,22 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.08493679991571336</v>
+        <v>-0.1128628071677499</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
         <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.005132296706541574</v>
+        <v>0.02940671068759908</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.107260316561954</v>
+        <v>0.05005876308788209</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
@@ -3548,100 +3548,100 @@
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.411111576022698e-05</v>
+        <v>-0.1176648399683078</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.01656313510158922</v>
+        <v>0.0987659328249483</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.02173635870421967</v>
+        <v>0.09696302121904032</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.06794519309467903</v>
+        <v>-0.1132667735478171</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
         <v>0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.002517826506811512</v>
+        <v>0.008266387471978583</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.1129463761574095</v>
+        <v>0.07134993351079165</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.04002326517017469</v>
+        <v>-0.04182103570936625</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0444566794875837</v>
+        <v>-0.1773522024170269</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.001614683906987056</v>
+        <v>0.05430905562071246</v>
       </c>
       <c r="DK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM6" t="n">
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.006081052987154392</v>
+        <v>-0.006789881564130029</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.03351720870604942</v>
+        <v>-0.06165173203514228</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.00651404814989466</v>
+        <v>0.07945600496514979</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
@@ -3650,13 +3650,13 @@
         <v>-0</v>
       </c>
       <c r="DV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW6" t="n">
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.05777594466092893</v>
+        <v>-0.0203989119697206</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,106 +3665,106 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01639577769065341</v>
+        <v>-0.0676568575607339</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.05440360332127209</v>
+        <v>0.03633715307927934</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
         <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.09693440032671177</v>
+        <v>-0.04598912915854268</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.02439302318152298</v>
+        <v>0.02204225341916105</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.1195640580710318</v>
+        <v>-0.009853383573066175</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
         <v>-0</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.02990216264525762</v>
+        <v>-0.005227696832770167</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
         <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01296633880913288</v>
+        <v>-0.01220162516658875</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.07094629067274934</v>
+        <v>0.1364584260180013</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.06543195927951648</v>
+        <v>-0.130932432158351</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
         <v>-0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.006229404879093165</v>
+        <v>-0.002061555924192711</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.1024537790435004</v>
+        <v>0.03987951912620769</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.002535719417640378</v>
+        <v>0.2075057372435904</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
@@ -3773,16 +3773,16 @@
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.008508884200727705</v>
+        <v>-0.08888362194263089</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.05172385674770193</v>
+        <v>0.1169911234280748</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
         <v>0</v>
@@ -3791,46 +3791,46 @@
         <v>0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.004963051982165477</v>
+        <v>0.01095474566180105</v>
       </c>
       <c r="FR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS6" t="n">
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.008810654514323803</v>
+        <v>-0.02433236845990461</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.03438754936987051</v>
+        <v>-0.04959525460895942</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
       </c>
       <c r="FW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.04462418624405818</v>
+        <v>-0.0392241248176862</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.05108333755087999</v>
+        <v>0.06229019800014492</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3839,7 +3839,7 @@
         <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1555227955103367</v>
+        <v>0.3740873085411197</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,25 +4994,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.08280241633837762</v>
+        <v>-0.01212069175337799</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.07228254118439849</v>
+        <v>-0.1420221622722794</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1280013609926359</v>
+        <v>0.4550155857997566</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,25 +5021,25 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.05768573777505789</v>
+        <v>-0.1030346101625517</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.07598714090533507</v>
+        <v>-0.1872297503630286</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01378244307605709</v>
+        <v>0.08850790259557874</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,40 +5048,40 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.004451178988662641</v>
+        <v>-0.08737791763617689</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009296517155136153</v>
+        <v>-0.01195679459117023</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.004937052603166965</v>
+        <v>-0.03445648712941773</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01397086337945391</v>
+        <v>-0.2456376296061947</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.01246458326384953</v>
+        <v>0.01208147322881906</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
@@ -5093,22 +5093,22 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01048426267962558</v>
+        <v>0.03864887039576933</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.008843058167262783</v>
+        <v>-0.03478953138166604</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.01472490147678882</v>
+        <v>0.004348853773135694</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
@@ -5117,28 +5117,28 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1072825700670186</v>
+        <v>0.4082565567656767</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.02880010261672456</v>
+        <v>-0.2569226983256364</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.02119212093019258</v>
+        <v>-0.1019174011449789</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>0</v>
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.03149636970574076</v>
+        <v>-0.007966828915457077</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,52 +5156,52 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.05775229627875221</v>
+        <v>0.003299825105484479</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.05909104473704765</v>
+        <v>-0.06672767056896817</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.03556435611813727</v>
+        <v>0.03790515352353375</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0160377211932141</v>
+        <v>0.05412149956945281</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01704690532514525</v>
+        <v>-0.02904912448350688</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.05103091105067987</v>
+        <v>0.2284431608214726</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.01218046926464564</v>
+        <v>-0.06484531704446789</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.01384008897907786</v>
+        <v>-0.108101791999787</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
@@ -5222,31 +5222,31 @@
         <v>-0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.02622308846222178</v>
+        <v>-0.106248834828522</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.007127736093176795</v>
+        <v>0.02637823890535754</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01772200217820961</v>
+        <v>0.05235108424751526</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>0</v>
@@ -5255,52 +5255,52 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0008607606247808709</v>
+        <v>-0.1167963372686887</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.007075855757484145</v>
+        <v>0.1418910920064637</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.01179765717120735</v>
+        <v>0.06948314519810558</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.01997228527183853</v>
+        <v>-0.1042914444843911</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.006098553888960175</v>
+        <v>0.01336787605902164</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.01817422480022265</v>
+        <v>0.07393732256271993</v>
       </c>
       <c r="DB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,22 +5309,22 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.03236358042313904</v>
+        <v>-0.07613463879940778</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.05139714038333401</v>
+        <v>-0.2088158290936235</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01369322867674388</v>
+        <v>0.0664830782668345</v>
       </c>
       <c r="DK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL9" t="n">
         <v>-0</v>
@@ -5333,28 +5333,28 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.005787316285419271</v>
+        <v>-0.01453139399809695</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.01937102480609069</v>
+        <v>-0.04380413370108927</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.009748317299426336</v>
+        <v>0.04598420032442908</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>-0</v>
@@ -5363,49 +5363,49 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.02951577427682513</v>
+        <v>-0.008128724834928856</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01498315768491325</v>
+        <v>-0.05739258479727879</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.01825960522851271</v>
+        <v>0.02186635189298738</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.0315053328593496</v>
+        <v>-0.04910027289638845</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.00944317674849344</v>
+        <v>0.009966225733988959</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.01334605781814872</v>
+        <v>-0.0008290111176221996</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5414,82 +5414,82 @@
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.01243019102766987</v>
+        <v>-0.03263751016830274</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.002243096035829807</v>
+        <v>-0.01666909488296208</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.01165242559899074</v>
+        <v>0.1081606505080878</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.0208915055260241</v>
+        <v>-0.1236182570442468</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.009264301360075101</v>
+        <v>0.001119420975175839</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.02170654796978215</v>
+        <v>0.04480882699908054</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>-0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.01511337365004362</v>
+        <v>0.1682489665630392</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0113268961668335</v>
+        <v>-0.08182097191585727</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.01985781488408164</v>
+        <v>0.1168730928665216</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
@@ -5498,63 +5498,63 @@
         <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>7.644719732458803e-05</v>
+        <v>0.001766033095943371</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.001509859052916248</v>
+        <v>-0.008890543018079875</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.01880918805336776</v>
+        <v>-0.02826654740530361</v>
       </c>
       <c r="FV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.001820653164314721</v>
+        <v>-0.03526500023485375</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.005457780234660795</v>
+        <v>0.06675703004937075</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
         <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1266462604957166</v>
+        <v>0.2568294364946774</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,10 +5563,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0359596502453245</v>
+        <v>0.08360029537802897</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1458807809284861</v>
+        <v>-0.1124021230301778</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -5575,10 +5575,10 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1005695273084039</v>
+        <v>0.2217196001047798</v>
       </c>
       <c r="K10" t="n">
         <v>-0</v>
@@ -5587,43 +5587,43 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.002737779122467324</v>
+        <v>-0.007165351043765546</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0997243053547566</v>
+        <v>-0.1079803910484537</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01760666690443216</v>
+        <v>-0.06928175277144705</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.03898100455986269</v>
+        <v>-0.04621480493013201</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.02367567826519899</v>
+        <v>-0.08056909819103956</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -5632,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.01516222809156062</v>
+        <v>0.0545615304003013</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -5641,43 +5641,43 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.02746700724001907</v>
+        <v>-0.03953367418522752</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.02875747820365326</v>
+        <v>0.05219803461472458</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.02170311454758471</v>
+        <v>0.01635961694893267</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.007094937415410008</v>
+        <v>0.0310684134670413</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.01299687962429524</v>
+        <v>0.01725490832228489</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -5686,25 +5686,25 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.08472652476482592</v>
+        <v>-0.0180578642833223</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.1007914678233191</v>
+        <v>0.08887558904301493</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.08600565149370705</v>
+        <v>-0.007113253437926324</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
         <v>0</v>
@@ -5713,22 +5713,22 @@
         <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.01499549256361632</v>
+        <v>0.1617831854512066</v>
       </c>
       <c r="BD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF10" t="n">
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.01190784752073141</v>
+        <v>-0.02019540684000256</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.04702454220862393</v>
+        <v>0.002295561210419389</v>
       </c>
       <c r="BI10" t="n">
         <v>0</v>
@@ -5740,10 +5740,10 @@
         <v>-0</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.007487808577764449</v>
+        <v>-0.06679451029213296</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,37 +5752,37 @@
         <v>0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.003610416424803363</v>
+        <v>-0.1113391538630767</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.008104688305153049</v>
+        <v>0.03653506681344443</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>0</v>
       </c>
       <c r="BT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.03643594286452657</v>
+        <v>-0.02642080760106553</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
       </c>
       <c r="BW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.03598242985426318</v>
+        <v>-0.0702652693062062</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.06421245250715174</v>
+        <v>-0.1104025499013803</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5791,10 +5791,10 @@
         <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0.02249073403637856</v>
+        <v>-0.06422544393623388</v>
       </c>
       <c r="CE10" t="n">
         <v>0</v>
@@ -5806,13 +5806,13 @@
         <v>0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.01066464430794283</v>
+        <v>0.007021126430780321</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.04343561869056956</v>
+        <v>0.03115380220022167</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
@@ -5821,25 +5821,25 @@
         <v>-0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.004126862283695319</v>
+        <v>0.01181028276288585</v>
       </c>
       <c r="CN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.06820944344543946</v>
+        <v>0.08373939567032432</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.001346799260798693</v>
+        <v>-0.04380478783386278</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
@@ -5848,7 +5848,7 @@
         <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0.02108001772460196</v>
+        <v>-0.06726026660128644</v>
       </c>
       <c r="CW10" t="n">
         <v>-0</v>
@@ -5860,40 +5860,40 @@
         <v>-0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.01460815439289092</v>
+        <v>0.004563328884568592</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.03937246904179714</v>
+        <v>0.03598994833441783</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
         <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0.0001534932277220459</v>
+        <v>-0.005146031250466448</v>
       </c>
       <c r="DF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG10" t="n">
         <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.03079357996395915</v>
+        <v>-0.06032322361351384</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.001550474019576347</v>
+        <v>0.01431398112090277</v>
       </c>
       <c r="DK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5902,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0.0005372762060466832</v>
+        <v>-0.03987372890085466</v>
       </c>
       <c r="DO10" t="n">
         <v>0</v>
@@ -5911,13 +5911,13 @@
         <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.03730876190525402</v>
+        <v>-0.05332094162376333</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.01723860783134225</v>
+        <v>0.08169112504517606</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
@@ -5926,37 +5926,37 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>-0.008746059748456648</v>
+        <v>0.02465871043844876</v>
       </c>
       <c r="DX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY10" t="n">
         <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.01650795672862657</v>
+        <v>0.1237911810008313</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.03860945368572078</v>
+        <v>0.06352424167544639</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE10" t="n">
         <v>0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0.02203262574153988</v>
+        <v>0.003466002153019663</v>
       </c>
       <c r="EG10" t="n">
         <v>0</v>
@@ -5968,22 +5968,22 @@
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>-0.003408451035381646</v>
+        <v>-0.02625681375732344</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.04728923408716374</v>
+        <v>0.0510532135942809</v>
       </c>
       <c r="EL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>-0.01277627041603102</v>
+        <v>-0.03844273207820576</v>
       </c>
       <c r="EP10" t="n">
         <v>0</v>
@@ -5992,13 +5992,13 @@
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.02803751493072065</v>
+        <v>0.006067814825159359</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.002817743768328517</v>
+        <v>0.04406886628997701</v>
       </c>
       <c r="EU10" t="n">
         <v>0</v>
@@ -6010,7 +6010,7 @@
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0.01808398236400945</v>
+        <v>-0.05967497713790787</v>
       </c>
       <c r="EY10" t="n">
         <v>0</v>
@@ -6022,22 +6022,22 @@
         <v>0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.02408577528846209</v>
+        <v>-0.006747037493913817</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.04115578127544132</v>
+        <v>0.04533085295682484</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.007376195651755181</v>
+        <v>0.127769368547643</v>
       </c>
       <c r="FH10" t="n">
         <v>-0</v>
@@ -6046,13 +6046,13 @@
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.01202097803954294</v>
+        <v>-5.861337664423544e-05</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0.002121784118489793</v>
+        <v>0.1059281336776556</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
@@ -6064,10 +6064,10 @@
         <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0006546982649096399</v>
+        <v>0.003074093359563177</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,13 +6076,13 @@
         <v>0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.0006216824476783274</v>
+        <v>0.001590208613466223</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.01139849522618542</v>
+        <v>0.04096364891334509</v>
       </c>
       <c r="FV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW10" t="n">
         <v>-0</v>
@@ -6091,28 +6091,28 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.00460258118434362</v>
+        <v>0.0725763631748053</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.01054367872908787</v>
+        <v>0.07896609230274053</v>
       </c>
       <c r="GE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
